--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けは、望んでおりませんでした。</t>
+          <t xml:space="preserve">こんな終わり方は、望んでおりませんでした。</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.polite[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.polite[1]</t>
+          <t xml:space="preserve">accepted.bold.polite[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残ります。まだここでやるべきことがあります</t>
+          <t xml:space="preserve">もっと大きな舞台で証明してみせます。…見ていてください</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.polite[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.polite[1]</t>
+          <t xml:space="preserve">accepted.bold.polite[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受け入れます。…ここまでやれたこと、誇りに思います</t>
+          <t xml:space="preserve">行かせていただきます。お世話になりました</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.polite[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.polite[1]</t>
+          <t xml:space="preserve">defended.bold.polite[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだです。まだやれます。もう少しだけ時間をください</t>
+          <t xml:space="preserve">そこまで仰るなら、残らせていただきます</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.polite[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.polite[1]</t>
+          <t xml:space="preserve">defended.bold.polite[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直に申し上げます。…もう限界です</t>
+          <t xml:space="preserve">簡単には手放さない、ということですか。…悪い気はしません</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.polite[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">defense_failed.bold.polite[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残ります。ここで頂点を目指させていただきますから</t>
+          <t xml:space="preserve">…申し訳ありません。ですが、わたしの決意は固いんです</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.polite[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3200,29 +3200,29 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.polite[1]</t>
+          <t xml:space="preserve">defense_failed.bold.polite[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。…ただ、もう少し条件を詰めさせてください</t>
+          <t xml:space="preserve">止められても止まりません。…失礼します</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.polite[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3232,29 +3232,29 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold.polite[1]</t>
+          <t xml:space="preserve">former_champ.bold.polite[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件を聞かせてください。それ次第です</t>
+          <t xml:space="preserve">残ります。まだここでやるべきことがあります</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.polite[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3264,29 +3264,29 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
+          <t xml:space="preserve">accept_terminal.bold.polite[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、私たちのメンバーをもう少し大切にしていただきたいです。</t>
+          <t xml:space="preserve">受け入れます。…ここまでやれたこと、誇りに思います</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.polite[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3296,29 +3296,29 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
+          <t xml:space="preserve">refuse_champ.bold.polite[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、次のメインを私たちに任せていただけないでしょうか。</t>
+          <t xml:space="preserve">まだです。まだやれます。もう少しだけ時間をください</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.polite[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3328,29 +3328,29 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
+          <t xml:space="preserve">A1_champion.bold.polite[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、私たちのメンバーの待遇を見直していただきたいです。</t>
+          <t xml:space="preserve">正直に申し上げます。…もう限界です</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.polite[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3360,29 +3360,29 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
+          <t xml:space="preserve">A2_uncrowned.bold.polite[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、私たちの貢献を一度きちんと評価していただきたく存じます。</t>
+          <t xml:space="preserve">どうしても勝てない相手がいました。それでも、逃げませんでした。…悔いはありません</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.polite[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3392,29 +3392,29 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
+          <t xml:space="preserve">A3_heel.bold.polite[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、何より励みになります。</t>
+          <t xml:space="preserve">最後まで嫌われ者でいさせていただきます。…最高でした</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.polite[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3424,29 +3424,29 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
+          <t xml:space="preserve">A4_veteran.bold.polite[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">長かったようで…あっという間でした。悔いはありません</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.polite[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
+          <t xml:space="preserve">B1_young.bold.polite[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">嘘です…まだ始まったばかりじゃありませんか…！</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.polite[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3488,29 +3488,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
+          <t xml:space="preserve">B2_prime.bold.polite[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。お任せいただいた以上、結果で示します。</t>
+          <t xml:space="preserve">まだやれると思っていました。信じていたんです…！</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.polite[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
+          <t xml:space="preserve">B3_older.bold.polite[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">体はもう限界です。…ですが、気持ちはまだ燃えています</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.polite[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3552,29 +3552,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
+          <t xml:space="preserve">B4_champion_injury.bold.polite[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">チャンピオンのまま怪我で終わる……これは幸運なのでしょうか、不運なのでしょうか……</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3584,29 +3584,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉以上の働きでお返しします。</t>
+          <t xml:space="preserve">残ります。ここで頂点を目指させていただきますから</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.polite[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3616,29 +3616,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
+          <t xml:space="preserve">raise_accept.bold.polite[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">……ありがとうございます。分かってくださる社長で助かります。今期も全力で参ります。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.polite[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3648,29 +3648,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.bold.polite[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">……ゼロでないのなら、お受けします。ですが次は、正当な評価を期待しております。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.polite[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3680,29 +3680,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.bold.polite[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、何よりの励みになります。</t>
+          <t xml:space="preserve">……そうですか。承知しました。ですが社長、次はないとお考えください。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.polite[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3712,29 +3712,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
+          <t xml:space="preserve">raise_open.bold.polite[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">ありがとうございます。…ただ、もう少し条件を詰めさせてください</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.polite[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3744,29 +3744,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
+          <t xml:space="preserve">raise_refuse.bold.polite[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">…………。そうですか、承知しました。ですが社長、我慢にも限度がございます。そのおつもりで。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.polite[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3776,29 +3776,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
+          <t xml:space="preserve">sudden_departure.bold.polite[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました、次はお声をかけさせていただきます。</t>
+          <t xml:space="preserve">社長、もう無理です。お世話になりました……と申し上げたいところですが、正直そうも思えません。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.polite[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3808,29 +3808,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
+          <t xml:space="preserve">sudden_departure.bold.polite[2]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも大切にします。</t>
+          <t xml:space="preserve">もう決めました。これ以上ここに残る理由がございません。失礼します。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.polite[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3840,29 +3840,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_listen.bold.polite[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。気をつけます。</t>
+          <t xml:space="preserve">……聞いてくださるんですか。{record}正直、もっと上の舞台で闘いたいんです。ここでは物足りなくて。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.polite[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3872,29 +3872,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_open.bold.polite[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">社長。{tenure}もう決めております。この団体を出させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.polite[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3904,29 +3904,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_open.bold.polite[2]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。営業に響くなら、線を引かせていただきます。</t>
+          <t xml:space="preserve">……はっきり申し上げます。{tenure}ここではもう伸びません。退団させてください。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.polite[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3936,29 +3936,29 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_release.bold.polite[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
+          <t xml:space="preserve">……ええ、そうなるだろうと思っておりました。{rivalry}失礼します、社長。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.polite[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3968,29 +3968,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.bold.polite[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑おかけしました。明日からきちんと出させていただきます。</t>
+          <t xml:space="preserve">……申し訳ありませんが、もう決めております。気持ちは変わりません。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.polite[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4000,29 +4000,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_retain_success.bold.polite[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、しっかり返します。</t>
+          <t xml:space="preserve">……仕方ありませんね。そこまでおっしゃるなら、もう少しだけお付き合いします。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.polite[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4032,29 +4032,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
+          <t xml:space="preserve">start.bold.polite[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">条件を聞かせてください。それ次第です</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4079,14 +4079,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お言葉に甘えて、少し休ませていただきます。</t>
+          <t xml:space="preserve">社長、突然ですが、私たちのメンバーをもう少し大切にしていただきたいです。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。問題ありません。</t>
+          <t xml:space="preserve">社長、突然ですが、次のメインを私たちに任せていただけないでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
+          <t xml:space="preserve">社長、突然ですが、私たちのメンバーの待遇を見直していただきたいです。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。私からメンバーに話させていただきます。</t>
+          <t xml:space="preserve">社長、突然ですが、私たちの貢献を一度きちんと評価していただきたく存じます。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便にいたします。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、何より励みになります。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子にも目を向けてくださって。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。改めます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…言葉を選ぶように、口を閉ざした）</t>
+          <t xml:space="preserve">ありがとうございます。お任せいただいた以上、結果で示します。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがたく承ります。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。怪我させては元も子もありません。緩めます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。このまま続けさせていただきます。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉以上の働きでお返しします。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく承ります。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.polite</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、同じ場所には立てません</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.polite</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4495,29 +4495,29 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等です。お受けいたします</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、何よりの励みになります。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありません。けれど、心は固まっております。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4544,29 +4544,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">手応えがあります。まだまだ伸びます</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4576,29 +4576,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しで掴めそうです。あと一歩です</t>
+          <t xml:space="preserve">…承知しました、次はお声をかけさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4608,29 +4608,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界を感じますが…まだやれることはあります</t>
+          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも大切にします。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ上があります。ここからが本当の戦いです</t>
+          <t xml:space="preserve">…承知しました。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4672,29 +4672,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですが、確実に前に進んでいます</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4704,29 +4704,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ました。…でもまだ、挑戦し続けます</t>
+          <t xml:space="preserve">…承知しました。営業に響くなら、線を引かせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4736,29 +4736,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目していただけるのは光栄です。期待に応えます</t>
+          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4768,29 +4768,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全ての応援に、試合で応えてみせます</t>
+          <t xml:space="preserve">…ご迷惑おかけしました。明日からきちんと出させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4800,29 +4800,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直…目標を見失いかけています</t>
+          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、しっかり返します。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4832,29 +4832,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目標が見えてきました。もう迷いません</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4864,29 +4864,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復調しました。もう大丈夫です</t>
+          <t xml:space="preserve">…ありがとうございます。お言葉に甘えて、少し休ませていただきます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4896,29 +4896,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、調子が上がりません。…でも、立て直します</t>
+          <t xml:space="preserve">…大丈夫です。問題ありません。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4928,29 +4928,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
+          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4960,29 +4960,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
+          <t xml:space="preserve">…承知しました。私からメンバーに話させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4992,29 +4992,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
+          <t xml:space="preserve">…ありがとうございます。穏便にいたします。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5024,29 +5024,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子にも目を向けてくださって。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5056,29 +5056,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで戦えること、心から感謝しております!</t>
+          <t xml:space="preserve">…承知しました。改めます。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5088,29 +5088,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で、この舞台に恥じない試合をします!</t>
+          <t xml:space="preserve">（…言葉を選ぶように、口を閉ざした）</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5120,29 +5120,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の期待に、必ず応えてみせます!</t>
+          <t xml:space="preserve">…ご配慮、ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5152,29 +5152,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に、心から感謝します!!</t>
+          <t xml:space="preserve">…承知しました。怪我させては元も子もありません。緩めます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5184,29 +5184,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で戦った甲斐がありました!!</t>
+          <t xml:space="preserve">…ありがとうございます。このまま続けさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5216,29 +5216,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この興奮、必ず次につなげます!!</t>
+          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.bold.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.polite</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5248,29 +5248,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.bold.polite[1]</t>
+          <t xml:space="preserve">bold.attack.polite</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、やりましたよ!わたしにできないことなんてない!</t>
+          <t xml:space="preserve">もう、同じ場所には立てません</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.polite</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5280,61 +5280,61 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">bold.defend.polite</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">上等です。お受けいたします</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">……申し訳ありません。けれど、心は固まっております。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
@@ -5354,19 +5354,19 @@
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">手応えがあります。まだまだ伸びます</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">BT_HINT_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5376,29 +5376,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">もう少しで掴めそうです。あと一歩です</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.polite[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5408,29 +5408,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.polite[1]</t>
+          <t xml:space="preserve">cap_reached.bold.polite[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">限界を感じますが…まだやれることはあります</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.polite[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.polite[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5440,29 +5440,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.polite[2]</t>
+          <t xml:space="preserve">ovr_elite.bold.polite[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">まだ上があります。ここからが本当の戦いです</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.polite[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5472,29 +5472,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.polite[1]</t>
+          <t xml:space="preserve">ovr_growth.bold.polite[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">まだまだですが、確実に前に進んでいます</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.polite[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.polite[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5504,29 +5504,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.polite[2]</t>
+          <t xml:space="preserve">ovr_legend.bold.polite[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">ここまで来ました。…でもまだ、挑戦し続けます</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.polite[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5536,29 +5536,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.polite[1]</t>
+          <t xml:space="preserve">pop_growth.bold.polite[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">注目していただけるのは光栄です。期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.polite[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.polite[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5568,29 +5568,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.polite[2]</t>
+          <t xml:space="preserve">pop_star.bold.polite[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">全ての応援に、試合で応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
@@ -5610,19 +5610,19 @@
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">正直…目標を見失いかけています</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5632,29 +5632,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">目標が見えてきました。もう迷いません</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5664,29 +5664,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
+          <t xml:space="preserve">復調しました。もう大丈夫です</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.polite[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,29 +5696,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">defeat.bold.polite[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
+          <t xml:space="preserve">正直、調子が上がりません。…でも、立て直します</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.polite[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,29 +5728,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">bestMatch.bold.polite[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
+          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.bold.polite[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.polite[1]</t>
+          <t xml:space="preserve">champion.bold.polite[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
+          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.polite[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5792,29 +5792,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.polite[2]</t>
+          <t xml:space="preserve">hallOfFame.bold.polite[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
+          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.bold.polite[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,29 +5824,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.polite[1]</t>
+          <t xml:space="preserve">mvp.bold.polite[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
+          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,29 +5856,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.polite[2]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
+          <t xml:space="preserve">ドームで戦えること、心から感謝しております!</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,29 +5888,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.polite[1]</t>
+          <t xml:space="preserve">bold.polite[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
+          <t xml:space="preserve">全力で、この舞台に恥じない試合をします!</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[3]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,29 +5920,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.polite[2]</t>
+          <t xml:space="preserve">bold.polite[3]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
+          <t xml:space="preserve">お客様の期待に、必ず応えてみせます!</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,29 +5952,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.polite[1]</t>
+          <t xml:space="preserve">bold.polite[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
+          <t xml:space="preserve">満員のお客様に、心から感謝します!!</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,29 +5984,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.polite[2]</t>
+          <t xml:space="preserve">bold.polite[2]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
+          <t xml:space="preserve">全力で戦った甲斐がありました!!</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[3]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,29 +6016,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.polite[1]</t>
+          <t xml:space="preserve">bold.polite[3]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
+          <t xml:space="preserve">この興奮、必ず次につなげます!!</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.polite[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.polite[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,29 +6048,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.polite[2]</t>
+          <t xml:space="preserve">faction_decree.bold.polite[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
+          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.polite[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,29 +6080,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.polite[1]</t>
+          <t xml:space="preserve">E1.bold.polite[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.polite[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.polite[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,29 +6112,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.polite[2]</t>
+          <t xml:space="preserve">E1.bold.polite[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+          <t xml:space="preserve">わたしが出れば注目は集まります。任せてください</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.bold.polite[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">E1.accept.bold.polite[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+          <t xml:space="preserve">やった、やりましたよ!わたしにできないことなんてない!</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.polite[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
@@ -6186,19 +6186,19 @@
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待っていました、この瞬間を……!わたしの力、証明できました!</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.polite[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6208,59 +6208,2683 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">bold.polite[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftInterest.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftInterest.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftJoin.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftJoin.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">合いません。どうしても合わないんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう終わったことです</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着はつきました。次に進みます</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">超えること。それが今の私の全てです</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.polite[2]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと待っていました、この瞬間を……!わたしの力、証明できました!</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.bold.polite[1]</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr" s="2">
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr" s="12">
+      <c r="D266" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.bold.polite[1]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr" s="2">
+      <c r="E266" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr" s="3">
+      <c r="F266" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
         </is>
       </c>
     </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.polite[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H186"/>
+  <autoFilter ref="A1:H268"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -342,7 +342,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.bold[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -357,7 +357,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.polite[1]</t>
+          <t xml:space="preserve">atk.polite.bold[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -374,7 +374,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.bold[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -389,7 +389,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.polite[2]</t>
+          <t xml:space="preserve">atk.polite.bold[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -406,7 +406,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.bold[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -421,7 +421,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.polite[3]</t>
+          <t xml:space="preserve">atk.polite.bold[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -438,7 +438,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.polite[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.bold[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -453,7 +453,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.polite[4]</t>
+          <t xml:space="preserve">atk.polite.bold[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.bold[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -485,7 +485,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.polite[1]</t>
+          <t xml:space="preserve">bigmove.polite.bold[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.bold[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -517,7 +517,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.polite[2]</t>
+          <t xml:space="preserve">bigmove.polite.bold[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.bold[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -549,7 +549,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.polite[3]</t>
+          <t xml:space="preserve">bigmove.polite.bold[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -566,7 +566,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.bold[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -581,7 +581,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.polite[1]</t>
+          <t xml:space="preserve">climax.polite.bold[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -598,7 +598,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.bold[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -613,7 +613,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.polite[2]</t>
+          <t xml:space="preserve">climax.polite.bold[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -630,7 +630,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -645,7 +645,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -662,7 +662,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -677,7 +677,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -726,7 +726,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -741,7 +741,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold.polite[1]</t>
+          <t xml:space="preserve">badWinner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -773,7 +773,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold.polite[1]</t>
+          <t xml:space="preserve">goodWinner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -790,7 +790,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -805,7 +805,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -822,7 +822,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -837,7 +837,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.polite[1]</t>
+          <t xml:space="preserve">loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -854,7 +854,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -869,7 +869,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.polite[1]</t>
+          <t xml:space="preserve">winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -886,7 +886,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.polite.bold[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -901,7 +901,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.polite[1]</t>
+          <t xml:space="preserve">competition_won.polite.bold[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -918,7 +918,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.polite.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -933,7 +933,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.polite[1]</t>
+          <t xml:space="preserve">direct.polite.bold[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -950,7 +950,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.polite.bold[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -965,7 +965,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.polite[1]</t>
+          <t xml:space="preserve">fa_signing.polite.bold[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -982,7 +982,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.polite.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.bold.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -997,7 +997,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite.hit[1]</t>
+          <t xml:space="preserve">polite.bold.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1014,7 +1014,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.polite.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.bold.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite.hit[2]</t>
+          <t xml:space="preserve">polite.bold.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1046,7 +1046,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.polite.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.bold.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite.win[1]</t>
+          <t xml:space="preserve">polite.bold.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1078,7 +1078,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.polite.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.bold.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite.win[2]</t>
+          <t xml:space="preserve">polite.bold.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1110,7 +1110,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1142,7 +1142,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1174,7 +1174,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1206,7 +1206,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1270,7 +1270,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1302,7 +1302,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1334,7 +1334,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1430,7 +1430,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1462,7 +1462,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1622,7 +1622,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.polite[1]</t>
+          <t xml:space="preserve">loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.polite[1]</t>
+          <t xml:space="preserve">winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.polite[1]</t>
+          <t xml:space="preserve">loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.polite[1]</t>
+          <t xml:space="preserve">winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1782,7 +1782,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.polite.bold[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.polite[1]</t>
+          <t xml:space="preserve">defender.polite.bold[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1814,7 +1814,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.polite.bold[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.polite[1]</t>
+          <t xml:space="preserve">defender.polite.bold[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1878,7 +1878,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.polite.bold[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.polite[1]</t>
+          <t xml:space="preserve">defender.polite.bold[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1942,7 +1942,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.bold.polite[1]</t>
+          <t xml:space="preserve">fateAttacker.polite.bold[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.polite.bold[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.bold.polite[1]</t>
+          <t xml:space="preserve">fateDefender.polite.bold[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2038,7 +2038,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2070,7 +2070,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.polite.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.bold.polite[1]</t>
+          <t xml:space="preserve">fateLoser.polite.bold[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.bold.polite[1]</t>
+          <t xml:space="preserve">fateWinner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.polite[1]</t>
+          <t xml:space="preserve">loser.polite.bold[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2166,7 +2166,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.polite[1]</t>
+          <t xml:space="preserve">winner.polite.bold[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2198,7 +2198,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2230,7 +2230,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.bold[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -3030,7 +3030,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.bold[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.polite[1]</t>
+          <t xml:space="preserve">accepted.polite.bold[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.polite[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.bold[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.polite[2]</t>
+          <t xml:space="preserve">accepted.polite.bold[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3094,7 +3094,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.bold[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.polite[1]</t>
+          <t xml:space="preserve">defended.polite.bold[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3126,7 +3126,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.polite[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.bold[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.polite[2]</t>
+          <t xml:space="preserve">defended.polite.bold[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3158,7 +3158,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.polite[1]</t>
+          <t xml:space="preserve">defense_failed.polite.bold[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3190,7 +3190,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.polite[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.bold[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.polite[2]</t>
+          <t xml:space="preserve">defense_failed.polite.bold[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3222,7 +3222,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.polite.bold[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.polite[1]</t>
+          <t xml:space="preserve">former_champ.polite.bold[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3254,7 +3254,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.polite.bold[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.polite.bold[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3286,7 +3286,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.polite.bold[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.polite.bold[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3318,7 +3318,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.polite[1]</t>
+          <t xml:space="preserve">A1_champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.polite.bold[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.polite.bold[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3382,7 +3382,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.polite.bold[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.polite[1]</t>
+          <t xml:space="preserve">A3_heel.polite.bold[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3414,7 +3414,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.polite.bold[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.polite.bold[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.polite.bold[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.polite[1]</t>
+          <t xml:space="preserve">B1_young.polite.bold[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.polite.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.polite[1]</t>
+          <t xml:space="preserve">B2_prime.polite.bold[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.polite.bold[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.polite[1]</t>
+          <t xml:space="preserve">B3_older.polite.bold[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3542,7 +3542,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.polite[1]</t>
+          <t xml:space="preserve">raise_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.polite[1]</t>
+          <t xml:space="preserve">raise_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3766,7 +3766,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3798,7 +3798,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.bold[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.polite[2]</t>
+          <t xml:space="preserve">sudden_departure.polite.bold[2]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3830,7 +3830,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3862,7 +3862,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.polite[1]</t>
+          <t xml:space="preserve">transfer_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3894,7 +3894,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.bold[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.polite[2]</t>
+          <t xml:space="preserve">transfer_open.polite.bold[2]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3926,7 +3926,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.polite[1]</t>
+          <t xml:space="preserve">transfer_release.polite.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3990,7 +3990,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4022,7 +4022,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold.polite[1]</t>
+          <t xml:space="preserve">start.polite.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -5302,39 +5302,39 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありません。けれど、心は固まっております。</t>
+          <t xml:space="preserve">手応えがあります。まだまだ伸びます</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">手応えがあります。まだまだ伸びます</t>
+          <t xml:space="preserve">もう少しで掴めそうです。あと一歩です</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">cap_reached.polite.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しで掴めそうです。あと一歩です</t>
+          <t xml:space="preserve">限界を感じますが…まだやれることはあります</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.polite[1]</t>
+          <t xml:space="preserve">ovr_elite.polite.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界を感じますが…まだやれることはあります</t>
+          <t xml:space="preserve">まだ上があります。ここからが本当の戦いです</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.polite[1]</t>
+          <t xml:space="preserve">ovr_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5455,14 +5455,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ上があります。ここからが本当の戦いです</t>
+          <t xml:space="preserve">まだまだですが、確実に前に進んでいます</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.polite[1]</t>
+          <t xml:space="preserve">ovr_legend.polite.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5487,14 +5487,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですが、確実に前に進んでいます</t>
+          <t xml:space="preserve">ここまで来ました。…でもまだ、挑戦し続けます</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.polite[1]</t>
+          <t xml:space="preserve">pop_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ました。…でもまだ、挑戦し続けます</t>
+          <t xml:space="preserve">注目していただけるのは光栄です。期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold.polite[1]</t>
+          <t xml:space="preserve">pop_star.polite.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目していただけるのは光栄です。期待に応えます</t>
+          <t xml:space="preserve">全ての応援に、試合で応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全ての応援に、試合で応えてみせます</t>
+          <t xml:space="preserve">正直…目標を見失いかけています</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直…目標を見失いかけています</t>
+          <t xml:space="preserve">目標が見えてきました。もう迷いません</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5647,14 +5647,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目標が見えてきました。もう迷いません</t>
+          <t xml:space="preserve">復調しました。もう大丈夫です</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">defeat.polite.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5679,14 +5679,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復調しました。もう大丈夫です</t>
+          <t xml:space="preserve">正直、調子が上がりません。…でも、立て直します</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,29 +5696,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.polite[1]</t>
+          <t xml:space="preserve">bestMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、調子が上がりません。…でも、立て直します</t>
+          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.polite[1]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
+          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
+          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.polite[1]</t>
+          <t xml:space="preserve">mvp.polite.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
+          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
+          <t xml:space="preserve">ドームで戦えること、心から感謝しております!</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで戦えること、心から感謝しております!</t>
+          <t xml:space="preserve">全力で、この舞台に恥じない試合をします!</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で、この舞台に恥じない試合をします!</t>
+          <t xml:space="preserve">お客様の期待に、必ず応えてみせます!</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5935,14 +5935,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の期待に、必ず応えてみせます!</t>
+          <t xml:space="preserve">満員のお客様に、心から感謝します!!</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に、心から感謝します!!</t>
+          <t xml:space="preserve">全力で戦った甲斐がありました!!</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で戦った甲斐がありました!!</t>
+          <t xml:space="preserve">この興奮、必ず次につなげます!!</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.polite[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,29 +6016,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[3]</t>
+          <t xml:space="preserve">faction_decree.polite.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この興奮、必ず次につなげます!!</t>
+          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold.polite[1]</t>
+          <t xml:space="preserve">E1.polite.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
+          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.polite[1]</t>
+          <t xml:space="preserve">E1.polite.bold[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6095,14 +6095,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
+          <t xml:space="preserve">わたしが出れば注目は集まります。任せてください</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.polite[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.polite[2]</t>
+          <t xml:space="preserve">E1.accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6127,14 +6127,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしが出れば注目は集まります。任せてください</t>
+          <t xml:space="preserve">やった、やりましたよ!わたしにできないことなんてない!</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、やりましたよ!わたしにできないことなんてない!</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">draftInterest.polite.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.polite[1]</t>
+          <t xml:space="preserve">draftInterest.polite.bold[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.polite[2]</t>
+          <t xml:space="preserve">draftJoin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.polite[1]</t>
+          <t xml:space="preserve">draftJoin.polite.bold[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.polite[2]</t>
+          <t xml:space="preserve">faGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold.polite[1]</t>
+          <t xml:space="preserve">faSigning.polite.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.polite[1]</t>
+          <t xml:space="preserve">faSigning.polite.bold[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.polite[2]</t>
+          <t xml:space="preserve">faWelcome.polite.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.polite[1]</t>
+          <t xml:space="preserve">faWelcome.polite.bold[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.polite[2]</t>
+          <t xml:space="preserve">injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.polite[1]</t>
+          <t xml:space="preserve">injury.polite.bold[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.polite[2]</t>
+          <t xml:space="preserve">release.polite.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.polite[1]</t>
+          <t xml:space="preserve">release.polite.bold[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.polite[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.polite[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.bold[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.polite[2]</t>
+          <t xml:space="preserve">scoutGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold.polite[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.polite[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.polite[2]</t>
+          <t xml:space="preserve">titleDefense.polite.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.polite[1]</t>
+          <t xml:space="preserve">titleDefense.polite.bold[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.polite[2]</t>
+          <t xml:space="preserve">titleLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.polite[1]</t>
+          <t xml:space="preserve">titleLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.polite[2]</t>
+          <t xml:space="preserve">titleWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.polite[1]</t>
+          <t xml:space="preserve">titleWin.polite.bold[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7616,29 +7616,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+          <t xml:space="preserve">合いません。どうしても合わないんです</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合いません。どうしても合わないんです</t>
+          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
+          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
+          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
+          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
+          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
+          <t xml:space="preserve">……もう終わったことです</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったことです</t>
+          <t xml:space="preserve">決着はつきました。次に進みます</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。次に進みます</t>
+          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
+          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
+          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
+          <t xml:space="preserve">超えること。それが今の私の全てです</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えること。それが今の私の全てです</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
+          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
+          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8111,14 +8111,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
+          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8175,14 +8175,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
+          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
+          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
+          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8288,29 +8288,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
+          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8335,14 +8335,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
+          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.polite[2]</t>
+          <t xml:space="preserve">preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8367,14 +8367,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
+          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
+          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.polite[2]</t>
+          <t xml:space="preserve">survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.polite[1]</t>
+          <t xml:space="preserve">survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
+          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.polite[2]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8495,14 +8495,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
+          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.polite[1]</t>
+          <t xml:space="preserve">champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
+          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.polite[2]</t>
+          <t xml:space="preserve">defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
+          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.polite[1]</t>
+          <t xml:space="preserve">defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8591,14 +8591,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
+          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.polite[2]</t>
+          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
+          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.polite[1]</t>
+          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.polite[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8672,12 +8672,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+          <t xml:space="preserve">全力で参ります。覚悟してください</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+          <t xml:space="preserve">ずっと待っていました、この瞬間を……!わたしの力、証明できました!</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待っていました、この瞬間を……!わたしの力、証明できました!</t>
+          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,29 +8768,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">fighter.polite.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold.polite[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,29 +8800,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold.polite[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8847,44 +8847,12 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="40" customHeight="1">
-      <c r="A268" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.polite[1]</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.polite[1]</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H268"/>
+  <autoFilter ref="A1:H267"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(丁寧×強気)に該当するキャラクター: 2名</t>
+          <t xml:space="preserve">このタイプ(丁寧×強気)に該当するキャラクター: 1名</t>
         </is>
       </c>
     </row>
@@ -235,7 +235,7 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">白銀麗子</t>
+          <t xml:space="preserve">大久保桃子</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -249,28 +249,6 @@
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">不屈、華、頑丈さ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">大久保桃子</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Allround</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Babyface</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">不屈、鉄人、頑丈さ</t>
         </is>
@@ -284,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -463,7 +441,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの全力、受けてくださいっ！</t>
+          <t xml:space="preserve">私の全力、受けてくださいっ！</t>
         </is>
       </c>
     </row>
@@ -591,7 +569,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ここからです…ここからが、わたしの時間）</t>
+          <t xml:space="preserve">（ここからです…ここからが、私の時間）</t>
         </is>
       </c>
     </row>
@@ -783,7 +761,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けられない試合でした。応えられて良かったです!</t>
+          <t xml:space="preserve">絶対に負けられない試合でした。応えられて良かったです！</t>
         </is>
       </c>
     </row>
@@ -911,7 +889,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを巡って争奪戦ですか。期待に応えさせていただきます</t>
+          <t xml:space="preserve">私を巡って争奪戦ですか。期待に応えさせていただきます</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1433,7 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの番ですっ！</t>
+          <t xml:space="preserve">私の番ですっ！</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2681,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだこと、後悔することになりますよ。</t>
+          <t xml:space="preserve">選ばれたからには、出し惜しみなしで！　全力で応えますよ。</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2937,7 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し上げた通りです。お相手が悪かったですね。</t>
+          <t xml:space="preserve">申し上げた通りです。最初から最後まで、全力で押し切りました。</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2969,7 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだのが、間違いでしたね。</t>
+          <t xml:space="preserve">ふぅ……出し切りました。これが今の実力です。</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3161,7 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。ですが、わたしの決意は固いんです</t>
+          <t xml:space="preserve">…申し訳ありません。ですが、私の決意は固いんです</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5273,7 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等です。お受けいたします</t>
+          <t xml:space="preserve">望むところです。お受けいたします</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5664,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5701,7 +5679,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5711,14 +5689,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
+          <t xml:space="preserve">この優勝は、団体全員で積み上げた力の証明です。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5733,7 +5711,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[1]</t>
+          <t xml:space="preserve">bestMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5721,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
+          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5765,7 +5743,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.bold[1]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5753,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
+          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5797,7 +5775,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5785,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
+          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,12 +5802,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">mvp.polite.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5839,14 +5817,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで戦えること、心から感謝しております!</t>
+          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,12 +5834,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">springTagChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5849,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で、この舞台に恥じない試合をします!</t>
+          <t xml:space="preserve">この優勝は、二人で準備してきた必然です。</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5893,7 +5871,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[3]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5903,14 +5881,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の期待に、必ず応えてみせます!</t>
+          <t xml:space="preserve">ドームで戦えること、心から感謝しております！</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,12 +5898,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5935,14 +5913,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に、心から感謝します!!</t>
+          <t xml:space="preserve">全力で、この舞台に恥じない試合をします！</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,12 +5930,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5967,14 +5945,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で戦った甲斐がありました!!</t>
+          <t xml:space="preserve">お客様の期待に、必ず応えてみせます！</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5989,7 +5967,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[3]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5999,14 +5977,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この興奮、必ず次につなげます!!</t>
+          <t xml:space="preserve">満員のお客様に、心から感謝します！！</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,29 +5994,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
+          <t xml:space="preserve">全力で戦った甲斐がありました！！</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,29 +6026,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
+          <t xml:space="preserve">この興奮、必ず次につなげます！！</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,12 +6058,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.bold[2]</t>
+          <t xml:space="preserve">faction_decree.polite.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6095,14 +6073,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしが出れば注目は集まります。任せてください</t>
+          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,12 +6090,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.polite.bold[1]</t>
+          <t xml:space="preserve">E1.polite.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6127,14 +6105,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、やりましたよ!わたしにできないことなんてない!</t>
+          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6122,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">E1.polite.bold[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+          <t xml:space="preserve">私が出れば注目は集まります。任せてください</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6176,29 +6154,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">E1.accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+          <t xml:space="preserve">やりました！　全力でぶつかれば、届くんですね！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6208,7 +6186,7 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
@@ -6223,14 +6201,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6240,7 +6218,7 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
@@ -6255,14 +6233,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,7 +6250,7 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
@@ -6287,14 +6265,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,7 +6282,7 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
@@ -6319,14 +6297,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,7 +6314,7 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
@@ -6351,14 +6329,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6368,7 +6346,7 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
@@ -6383,14 +6361,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,7 +6378,7 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
@@ -6415,14 +6393,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,7 +6410,7 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
@@ -6447,14 +6425,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,12 +6442,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6457,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,12 +6474,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6511,14 +6489,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6533,7 +6511,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.bold[1]</t>
+          <t xml:space="preserve">draftInterest.polite.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6543,14 +6521,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6565,7 +6543,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.bold[2]</t>
+          <t xml:space="preserve">draftInterest.polite.bold[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6575,14 +6553,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6597,7 +6575,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">draftJoin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6585,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6629,7 +6607,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.bold[1]</t>
+          <t xml:space="preserve">draftJoin.polite.bold[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6617,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6661,7 +6639,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.bold[2]</t>
+          <t xml:space="preserve">faGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6649,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6693,7 +6671,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.bold[1]</t>
+          <t xml:space="preserve">faSigning.polite.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6681,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6725,7 +6703,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.bold[2]</t>
+          <t xml:space="preserve">faSigning.polite.bold[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6713,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6757,7 +6735,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.bold[1]</t>
+          <t xml:space="preserve">faWelcome.polite.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6745,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6789,7 +6767,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.bold[2]</t>
+          <t xml:space="preserve">faWelcome.polite.bold[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6777,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6821,7 +6799,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.bold[1]</t>
+          <t xml:space="preserve">injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6809,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6853,7 +6831,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.bold[2]</t>
+          <t xml:space="preserve">injury.polite.bold[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6841,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6885,7 +6863,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">release.polite.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6873,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6917,7 +6895,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.bold[2]</t>
+          <t xml:space="preserve">release.polite.bold[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6905,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6927,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6937,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6981,7 +6959,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.bold[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6969,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7013,7 +6991,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.bold[2]</t>
+          <t xml:space="preserve">scoutGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7001,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7045,7 +7023,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7055,14 +7033,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7077,7 +7055,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.bold[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7087,14 +7065,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7087,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.bold[1]</t>
+          <t xml:space="preserve">titleDefense.polite.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7097,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7119,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.bold[2]</t>
+          <t xml:space="preserve">titleDefense.polite.bold[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7129,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7151,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.bold[1]</t>
+          <t xml:space="preserve">titleLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7161,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7183,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.bold[2]</t>
+          <t xml:space="preserve">titleLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7193,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7232,12 +7210,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">titleWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7225,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7264,12 +7242,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">titleWin.polite.bold[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7257,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7296,7 +7274,7 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
@@ -7311,14 +7289,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7328,7 +7306,7 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
@@ -7343,14 +7321,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,7 +7338,7 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
@@ -7375,14 +7353,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,7 +7370,7 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
@@ -7407,14 +7385,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7424,7 +7402,7 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
@@ -7439,14 +7417,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7456,7 +7434,7 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
@@ -7471,14 +7449,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7488,7 +7466,7 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
@@ -7503,14 +7481,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7520,7 +7498,7 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
@@ -7535,14 +7513,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7552,7 +7530,7 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
@@ -7567,14 +7545,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7584,7 +7562,7 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
@@ -7599,14 +7577,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7616,29 +7594,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合いません。どうしても合わないんです</t>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7648,29 +7626,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7685,7 +7663,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7673,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
+          <t xml:space="preserve">合いません。どうしても合わないんです</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7717,7 +7695,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7705,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
+          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7749,7 +7727,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7737,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
+          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7781,7 +7759,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7769,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
+          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7813,7 +7791,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7801,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったことです</t>
+          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7845,7 +7823,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7833,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。次に進みます</t>
+          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7877,7 +7855,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7865,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
+          <t xml:space="preserve">……もう終わったことです</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7909,7 +7887,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7897,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
+          <t xml:space="preserve">決着はつきました。次に進みます</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7941,7 +7919,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7929,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
+          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7973,7 +7951,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7961,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えること。それが今の私の全てです</t>
+          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8005,7 +7983,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +7993,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
+          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8037,7 +8015,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8025,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
+          <t xml:space="preserve">超えること。それが今の私の全てです</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8069,7 +8047,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8079,14 +8057,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8101,7 +8079,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8111,14 +8089,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
+          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8133,7 +8111,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8143,14 +8121,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
+          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8165,7 +8143,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8175,14 +8153,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8197,7 +8175,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8207,14 +8185,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
+          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8229,7 +8207,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8239,14 +8217,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
+          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,12 +8234,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8271,14 +8249,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
+          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8288,29 +8266,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8320,29 +8298,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
+          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8357,7 +8335,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.bold[1]</t>
+          <t xml:space="preserve">preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8367,14 +8345,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
+          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8389,7 +8367,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.bold[2]</t>
+          <t xml:space="preserve">preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8399,14 +8377,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
+          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8421,7 +8399,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.bold[1]</t>
+          <t xml:space="preserve">preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8431,14 +8409,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
+          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8453,7 +8431,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.bold[2]</t>
+          <t xml:space="preserve">preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8463,14 +8441,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
+          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8480,12 +8458,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[1]</t>
+          <t xml:space="preserve">survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8495,14 +8473,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8512,12 +8490,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[2]</t>
+          <t xml:space="preserve">survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8527,14 +8505,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
+          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8549,7 +8527,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.bold[1]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8559,14 +8537,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
+          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8581,7 +8559,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.bold[2]</t>
+          <t xml:space="preserve">champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8591,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
+          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8591,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
+          <t xml:space="preserve">defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8623,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
+          <t xml:space="preserve">defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8672,12 +8650,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8704,12 +8682,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待っていました、この瞬間を……!わたしの力、証明できました!</t>
+          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8736,7 +8714,7 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
@@ -8751,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+          <t xml:space="preserve">全力で参ります。覚悟してください</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,29 +8746,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+          <t xml:space="preserve">ずっと待っていました、この瞬間を……！私の力、証明できました！</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,7 +8778,7 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
@@ -8810,49 +8788,113 @@
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr" s="2">
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr" s="12">
+      <c r="D269" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr" s="2">
+      <c r="E269" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr" s="3">
+      <c r="F269" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H267"/>
+  <autoFilter ref="A1:H269"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3584,7 +3584,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.polite.bold[1]</t>
+          <t xml:space="preserve">decline_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3609,14 +3609,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。分かってくださる社長で助かります。今期も全力で参ります。</t>
+          <t xml:space="preserve">その額で構いません。悔しさに値段がついたと思えば、来年の張り合いになります。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.polite.bold[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.polite.bold[1]</t>
+          <t xml:space="preserve">decline_hold.polite.bold[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ゼロでないのなら、お受けします。ですが次は、正当な評価を期待しております。</t>
+          <t xml:space="preserve">据え置き……ですか。ではその差額ぶん、来年こちらから利子をつけてお返しします。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.polite.bold[1]</t>
+          <t xml:space="preserve">decline_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうですか。承知しました。ですが社長、次はないとお考えください。</t>
+          <t xml:space="preserve">はっきり言ってください。数字が下がる理由も、上げ直す道も、全部。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.polite.bold[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.polite.bold[1]</t>
+          <t xml:space="preserve">decline_strict.polite.bold[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。…ただ、もう少し条件を詰めさせてください</t>
+          <t xml:space="preserve">結構です。ここまで削ったのなら、こちらも遠慮はしません。取り返しにいきます。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.polite.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………。そうですか、承知しました。ですが社長、我慢にも限度がございます。そのおつもりで。</t>
+          <t xml:space="preserve">話が早くて助かります。次に上げてもらうときは、こちらから胸を張って言いにきますから。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.polite.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.polite.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、もう無理です。お世話になりました……と申し上げたいところですが、正直そうも思えません。</t>
+          <t xml:space="preserve">下げろと言ったのはこちらですよ。……いいでしょう。その値段に見合う一年にします。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.bold[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.bold[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう決めました。これ以上ここに残る理由がございません。失礼します。</t>
+          <t xml:space="preserve">今年は下げてください。動ける量が落ちたのは事実です。事実に値段をつけるのが査定でしょう。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.polite.bold[1]</t>
+          <t xml:space="preserve">raise_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくださるんですか。{record}正直、もっと上の舞台で闘いたいんです。ここでは物足りなくて。</t>
+          <t xml:space="preserve">……ありがとうございます。分かってくださる社長で助かります。今期も全力で参ります。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3865,14 +3865,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}もう決めております。この団体を出させていただきます。</t>
+          <t xml:space="preserve">……ゼロでないのなら、お受けします。ですが次は、正当な評価を期待しております。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.bold[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.bold[2]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はっきり申し上げます。{tenure}ここではもう伸びません。退団させてください。</t>
+          <t xml:space="preserve">……そうですか。承知しました。ですが社長、次はないとお考えください。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.polite.bold[1]</t>
+          <t xml:space="preserve">raise_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ、そうなるだろうと思っておりました。{rivalry}失礼します、社長。</t>
+          <t xml:space="preserve">ありがとうございます。…ただ、もう少し条件を詰めさせてください</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.polite.bold[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありませんが、もう決めております。気持ちは変わりません。</t>
+          <t xml:space="preserve">…………。そうですか、承知しました。ですが社長、我慢にも限度がございます。そのおつもりで。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.polite.bold[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仕方ありませんね。そこまでおっしゃるなら、もう少しだけお付き合いします。</t>
+          <t xml:space="preserve">社長、もう無理です。お世話になりました……と申し上げたいところですが、正直そうも思えません。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.bold[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.polite.bold[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.bold[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件を聞かせてください。それ次第です</t>
+          <t xml:space="preserve">もう決めました。これ以上ここに残る理由がございません。失礼します。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4042,29 +4042,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、私たちのメンバーをもう少し大切にしていただきたいです。</t>
+          <t xml:space="preserve">……聞いてくださるんですか。{record}正直、もっと上の舞台で闘いたいんです。ここでは物足りなくて。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4074,29 +4074,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_open.polite.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、次のメインを私たちに任せていただけないでしょうか。</t>
+          <t xml:space="preserve">社長。{tenure}もう決めております。この団体を出させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.bold[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,29 +4106,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_open.polite.bold[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、私たちのメンバーの待遇を見直していただきたいです。</t>
+          <t xml:space="preserve">……はっきり申し上げます。{tenure}ここではもう伸びません。退団させてください。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,29 +4138,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_release.polite.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、突然ですが、私たちの貢献を一度きちんと評価していただきたく存じます。</t>
+          <t xml:space="preserve">……ええ、そうなるだろうと思っておりました。{rivalry}失礼します、社長。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,29 +4170,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、何より励みになります。</t>
+          <t xml:space="preserve">……申し訳ありませんが、もう決めております。気持ちは変わりません。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4202,29 +4202,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">……仕方ありませんね。そこまでおっしゃるなら、もう少しだけお付き合いします。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4234,29 +4234,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
+          <t xml:space="preserve">start.polite.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">条件を聞かせてください。それ次第です</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.bold[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4281,14 +4281,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。お任せいただいた以上、結果で示します。</t>
+          <t xml:space="preserve">社長、突然ですが、私たちのメンバーをもう少し大切にしていただきたいです。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.bold[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4313,14 +4313,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">社長、突然ですが、次のメインを私たちに任せていただけないでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.bold[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">社長、突然ですが、私たちのメンバーの待遇を見直していただきたいです。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.bold[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4377,14 +4377,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉以上の働きでお返しします。</t>
+          <t xml:space="preserve">社長、突然ですが、私たちの貢献を一度きちんと評価していただきたく存じます。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、何より励みになります。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、何よりの励みになります。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
+          <t xml:space="preserve">ありがとうございます。お任せいただいた以上、結果で示します。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました、次はお声をかけさせていただきます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも大切にします。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉以上の働きでお返しします。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。気をつけます。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。営業に響くなら、線を引かせていただきます。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、何よりの励みになります。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
+          <t xml:space="preserve">…承知しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑おかけしました。明日からきちんと出させていただきます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、しっかり返します。</t>
+          <t xml:space="preserve">…承知しました、次はお声をかけさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
+          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも大切にします。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お言葉に甘えて、少し休ませていただきます。</t>
+          <t xml:space="preserve">…承知しました。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。問題ありません。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
+          <t xml:space="preserve">…承知しました。営業に響くなら、線を引かせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。私からメンバーに話させていただきます。</t>
+          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便にいたします。</t>
+          <t xml:space="preserve">…ご迷惑おかけしました。明日からきちんと出させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子にも目を向けてくださって。</t>
+          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、しっかり返します。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。改めます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…言葉を選ぶように、口を閉ざした）</t>
+          <t xml:space="preserve">…ありがとうございます。お言葉に甘えて、少し休ませていただきます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがたく承ります。</t>
+          <t xml:space="preserve">…大丈夫です。問題ありません。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。怪我させては元も子もありません。緩めます。</t>
+          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。このまま続けさせていただきます。</t>
+          <t xml:space="preserve">…承知しました。私からメンバーに話させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく承ります。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便にいたします。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、同じ場所には立てません</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子にも目を向けてくださって。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">望むところです。お受けいたします</t>
+          <t xml:space="preserve">…承知しました。改めます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">手応えがあります。まだまだ伸びます</t>
+          <t xml:space="preserve">（…言葉を選ぶように、口を閉ざした）</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しで掴めそうです。あと一歩です</t>
+          <t xml:space="preserve">…ご配慮、ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界を感じますが…まだやれることはあります</t>
+          <t xml:space="preserve">…承知しました。怪我させては元も子もありません。緩めます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ上があります。ここからが本当の戦いです</t>
+          <t xml:space="preserve">…ありがとうございます。このまま続けさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.polite.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですが、確実に前に進んでいます</t>
+          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく承ります。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.polite</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.polite.bold[1]</t>
+          <t xml:space="preserve">bold.attack.polite</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ました。…でもまだ、挑戦し続けます</t>
+          <t xml:space="preserve">もう、同じ場所には立てません</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.polite</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.polite.bold[1]</t>
+          <t xml:space="preserve">bold.defend.polite</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目していただけるのは光栄です。期待に応えます</t>
+          <t xml:space="preserve">望むところです。お受けいたします</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.bold[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全ての応援に、試合で応えてみせます</t>
+          <t xml:space="preserve">手応えがあります。まだまだ伸びます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直…目標を見失いかけています</t>
+          <t xml:space="preserve">もう少しで掴めそうです。あと一歩です</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">cap_reached.polite.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5593,14 +5593,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目標が見えてきました。もう迷いません</t>
+          <t xml:space="preserve">限界を感じますが…まだやれることはあります</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">ovr_elite.polite.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復調しました。もう大丈夫です</t>
+          <t xml:space="preserve">まだ上があります。ここからが本当の戦いです</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.polite.bold[1]</t>
+          <t xml:space="preserve">ovr_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5657,14 +5657,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、調子が上がりません。…でも、立て直します</t>
+          <t xml:space="preserve">まだまだですが、確実に前に進んでいます</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.polite.bold[1]</t>
+          <t xml:space="preserve">ovr_legend.polite.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝は、団体全員で積み上げた力の証明です。</t>
+          <t xml:space="preserve">ここまで来ました。…でもまだ、挑戦し続けます</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.bold[1]</t>
+          <t xml:space="preserve">pop_growth.polite.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
+          <t xml:space="preserve">注目していただけるのは光栄です。期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[1]</t>
+          <t xml:space="preserve">pop_star.polite.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
+          <t xml:space="preserve">全ての応援に、試合で応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
+          <t xml:space="preserve">正直…目標を見失いかけています</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
+          <t xml:space="preserve">目標が見えてきました。もう迷いません</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.bold[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝は、二人で準備してきた必然です。</t>
+          <t xml:space="preserve">復調しました。もう大丈夫です</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">defeat.polite.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで戦えること、心から感謝しております！</t>
+          <t xml:space="preserve">正直、調子が上がりません。…でも、立て直します</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で、この舞台に恥じない試合をします！</t>
+          <t xml:space="preserve">この優勝は、団体全員で積み上げた力の証明です。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[3]</t>
+          <t xml:space="preserve">bestMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5945,14 +5945,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の期待に、必ず応えてみせます！</t>
+          <t xml:space="preserve">当然の結果です。…でも、まだ上があります</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5977,14 +5977,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に、心から感謝します！！</t>
+          <t xml:space="preserve">ベルトを守り抜きました。…来年もこの座は譲りません</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">hallOfFame.polite.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で戦った甲斐がありました！！</t>
+          <t xml:space="preserve">殿堂入りです。…ここまで来ることができました</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[3]</t>
+          <t xml:space="preserve">mvp.polite.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この興奮、必ず次につなげます！！</t>
+          <t xml:space="preserve">当然です。…でも、来年も狙います</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.polite.bold[1]</t>
+          <t xml:space="preserve">springTagChampion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
+          <t xml:space="preserve">この優勝は、二人で準備してきた必然です。</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,29 +6090,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
+          <t xml:space="preserve">ドームで戦えること、心から感謝しております！</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,29 +6122,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が出れば注目は集まります。任せてください</t>
+          <t xml:space="preserve">全力で、この舞台に恥じない試合をします！</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました！　全力でぶつかれば、届くんですね！</t>
+          <t xml:space="preserve">お客様の期待に、必ず応えてみせます！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
@@ -6196,19 +6196,19 @@
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+          <t xml:space="preserve">満員のお客様に、心から感謝します！！</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
@@ -6228,19 +6228,19 @@
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+          <t xml:space="preserve">全力で戦った甲斐がありました！！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.bold[3]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[3]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">この興奮、必ず次につなげます！！</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,29 +6282,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">faction_decree.polite.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">従います。ですが、間違っているとは思っていません</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,29 +6314,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">E1.polite.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ行きたいんです</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.bold[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6346,29 +6346,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">E1.polite.bold[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+          <t xml:space="preserve">私が出れば注目は集まります。任せてください</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6378,29 +6378,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">E1.accept.polite.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+          <t xml:space="preserve">やりました！　全力でぶつかれば、届くんですね！</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6425,14 +6425,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6521,14 +6521,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに、必ずなります</t>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.bold[1]</t>
+          <t xml:space="preserve">draftInterest.polite.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
+          <t xml:space="preserve">頂点を獲ります。それ以外に興味はありません</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.bold[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.bold[2]</t>
+          <t xml:space="preserve">draftInterest.polite.bold[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
+          <t xml:space="preserve">選んでいただけたら、決して後悔はさせません</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.bold[1]</t>
+          <t xml:space="preserve">draftJoin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
+          <t xml:space="preserve">てっぺんを獲るために参りました。全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.bold[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.bold[2]</t>
+          <t xml:space="preserve">draftJoin.polite.bold[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6841,14 +6841,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まる気はありません</t>
+          <t xml:space="preserve">チャンピオンに、必ずなります</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.bold[1]</t>
+          <t xml:space="preserve">faGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6873,14 +6873,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.bold[2]</t>
+          <t xml:space="preserve">faSigning.polite.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6905,14 +6905,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">頂点を獲るために来ました。おわかりですよね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.bold[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">faSigning.polite.bold[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6937,14 +6937,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+          <t xml:space="preserve">新しい闘いの場ですね…！燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.bold[2]</t>
+          <t xml:space="preserve">faWelcome.polite.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+          <t xml:space="preserve">頂点まで一直線です。邪魔はさせません</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.bold[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.bold[1]</t>
+          <t xml:space="preserve">faWelcome.polite.bold[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7001,14 +7001,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
+          <t xml:space="preserve">燃えてきました…！早く試合がしたいです</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.bold[1]</t>
+          <t xml:space="preserve">injury.polite.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+          <t xml:space="preserve">ご心配なく。必ず戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.bold[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.bold[2]</t>
+          <t xml:space="preserve">injury.polite.bold[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+          <t xml:space="preserve">この程度で止まる気はありません</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.bold[1]</t>
+          <t xml:space="preserve">release.polite.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.bold[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.bold[2]</t>
+          <t xml:space="preserve">release.polite.bold[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.bold[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.bold[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.bold[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+          <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.bold[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7257,14 +7257,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">titleDefense.polite.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.bold[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">titleDefense.polite.bold[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7353,14 +7353,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">titleLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">titleLoss.polite.bold[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7417,14 +7417,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">titleWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7449,14 +7449,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.bold[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">titleWin.polite.bold[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7481,14 +7481,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7513,14 +7513,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
+          <t xml:space="preserve">悔しいです…次の場所で、必ず証明してみせます</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
+          <t xml:space="preserve">このままでは終わりません。どこかで必ず</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7577,14 +7577,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
+          <t xml:space="preserve">レンタルだからと侮らないでください。全試合全力です</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7609,14 +7609,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
+          <t xml:space="preserve">よその団体でも闘志は変わりません。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7641,14 +7641,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
+          <t xml:space="preserve">こんな結果、認められません…！もう一度やらせてください</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7658,29 +7658,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合いません。どうしても合わないんです</t>
+          <t xml:space="preserve">…今日は認めます。でも、この借りは必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7690,29 +7690,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
+          <t xml:space="preserve">まだ誰にもこの座はお譲りできません。もっと来てください</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7722,29 +7722,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
+          <t xml:space="preserve">防衛は通過点です。私が目指すのは、もっと先</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7754,29 +7754,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
+          <t xml:space="preserve">嘘です…！私のベルトが…！絶対に取り返します</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7786,29 +7786,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
+          <t xml:space="preserve">ベルトを失いました…でも、この悔しさが次の炎になります</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7818,29 +7818,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
+          <t xml:space="preserve">頂点に立ちました。でもまだ足りません…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.bold[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7850,29 +7850,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
+          <t xml:space="preserve">polite.bold[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったことです</t>
+          <t xml:space="preserve">この炎は消えません。このベルトで、もっと熱い闘いを</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。次に進みます</t>
+          <t xml:space="preserve">合いません。どうしても合わないんです</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
+          <t xml:space="preserve">これ以上は難しいです。それだけのことです</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
+          <t xml:space="preserve">壁を作られている気がします。少し面白くありません</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
+          <t xml:space="preserve">以前はもっとお話ししていたのに。…どうしてでしょう</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えること。それが今の私の全てです</t>
+          <t xml:space="preserve">信頼関係が築けそうです。心強いですね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8057,14 +8057,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
+          <t xml:space="preserve">二人なら、どんな困難も乗り越えられます</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
+          <t xml:space="preserve">……もう終わったことです</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.polite[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
+          <t xml:space="preserve">決着はつきました。次に進みます</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8153,14 +8153,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
+          <t xml:space="preserve">面白い方です。必ず超えてみせます</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8185,14 +8185,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
+          <t xml:space="preserve">ようやく手応えのある相手が現れました</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
+          <t xml:space="preserve">全力を出せる相手です。最高の敵ですね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
+          <t xml:space="preserve">超えること。それが今の私の全てです</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝しています…でも負けません</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.polite[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
+          <t xml:space="preserve">この戦いは生涯続くでしょう。望むところです</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8330,29 +8330,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.bold[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.polite[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
+          <t xml:space="preserve">ここが最高の場所です。私がもっと強くしてみせます</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.polite[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.bold[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.polite[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできています</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.polite[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
+          <t xml:space="preserve">ふざけないでください。私の価値がわからないなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.polite[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,29 +8426,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.bold[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.polite[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
+          <t xml:space="preserve">この扱いは許せません。覚えておいてください</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8458,29 +8458,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.polite[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
+          <t xml:space="preserve">この扱いは何でしょう。私の実力、ご存じないんですか</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.polite[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.bold[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.polite[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれません</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8522,29 +8522,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[1]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
+          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[2]</t>
+          <t xml:space="preserve">preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
+          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.bold[1]</t>
+          <t xml:space="preserve">preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
+          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.bold[2]</t>
+          <t xml:space="preserve">preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
+          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
+          <t xml:space="preserve">preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
+          <t xml:space="preserve">survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待っていました、この瞬間を……！私の力、証明できました！</t>
+          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8810,29 +8810,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.bold[1]</t>
+          <t xml:space="preserve">defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8842,59 +8842,283 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと待っていました、この瞬間を……！私の力、証明できました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr" s="2">
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr" s="12">
+      <c r="D276" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr" s="2">
+      <c r="E276" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr" s="3">
+      <c r="F276" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H269"/>
+  <autoFilter ref="A1:H276"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H273"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8288,7 +8288,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
+          <t xml:space="preserve">負けたけど……!わたし、全部出した!</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8330,29 +8330,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.bold[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.polite.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
+          <t xml:space="preserve">見ろよ!!これがわたしだ!!</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.bold[2]</t>
+          <t xml:space="preserve">GL-01.loss.polite.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
+          <t xml:space="preserve">くそっ……!こんなはず、じゃなかったのに……っ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.bold[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
+          <t xml:space="preserve">よっしゃ……!まだ終わらない!</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,29 +8426,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.bold[2]</t>
+          <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
+          <t xml:space="preserve">連勝は終わりましたが、まだまだこれからです</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.bold[1]</t>
+          <t xml:space="preserve">preFinal.polite.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
+          <t xml:space="preserve">身体は限界ですが、退きません。最後まで、押し通します</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.bold[2]</t>
+          <t xml:space="preserve">preFinal.polite.bold[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8505,14 +8505,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
+          <t xml:space="preserve">ここまで繋いだ分、最後は私が獲ります。痛みは、後で数えます</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[1]</t>
+          <t xml:space="preserve">preMatch.polite.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8537,14 +8537,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
+          <t xml:space="preserve">相手がどなたでも、全力で止めます。ここを通すわけにはいきませんので</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.bold[2]</t>
+          <t xml:space="preserve">preMatch.polite.bold[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
+          <t xml:space="preserve">誰が立ちはだかろうと、私のやることは変わりません。押し通ります</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.bold[1]</t>
+          <t xml:space="preserve">survivor.polite.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方、来てください</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.bold[2]</t>
+          <t xml:space="preserve">survivor.polite.bold[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
+          <t xml:space="preserve">まだ立ってます。ここは通しません。次、どうぞ全力で</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
+          <t xml:space="preserve">champion.polite.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
+          <t xml:space="preserve">この三人が一番強かったです。結果が全てを語っています</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
+          <t xml:space="preserve">champion.polite.bold[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
+          <t xml:space="preserve">仲間と一緒に勝てたことが、何より誇らしいです。最高のチームでした</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">defiant.polite.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参ります。覚悟してください</t>
+          <t xml:space="preserve">賞はいただきます。でも、次は優勝旗も一緒に持ち帰ります</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">defiant.polite.bold[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと待っていました、この瞬間を……！私の力、証明できました！</t>
+          <t xml:space="preserve">足りませんでした。次こそは、団体ごと勝ちます。必ず</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.bold[1]</t>
+          <t xml:space="preserve">gauntlet.polite.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+          <t xml:space="preserve">何人来ても、倒します。それが今日の答えでした</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.bold[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8810,29 +8810,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.bold[1]</t>
+          <t xml:space="preserve">gauntlet.polite.bold[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+          <t xml:space="preserve">限界は何度も見えました。でも、引く理由がないなら、前に出るだけです</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
@@ -8852,49 +8852,177 @@
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+          <t xml:space="preserve">全力で参ります。覚悟してください</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと待っていました、この瞬間を……！私の力、証明できました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。この団体の力を見せつけられたと思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで戦い抜けました。…悔いはありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.bold[1]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私を要らないと言った人たちに、見せつけてやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.bold[1]</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr" s="2">
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr" s="12">
+      <c r="D273" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.bold[1]</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr" s="2">
+      <c r="E273" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr" s="3">
+      <c r="F273" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見込まれた以上、結果は出します。必ず</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H269"/>
+  <autoFilter ref="A1:H273"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの方とやります。許可をください。</t>
+          <t xml:space="preserve">社長、三人であちらへ行きます。許可をください。</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めてきました。あの方と、やらせてください。</t>
+          <t xml:space="preserve">決めてきました。三人で、乗り込ませてください。</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず勝ちます。あの方との試合、通してください。</t>
+          <t xml:space="preserve">必ず勝ちます。三人での遠征、通してください。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×強気.xlsx
@@ -8537,7 +8537,7 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど……!わたし、全部出した!</t>
+          <t xml:space="preserve">負けました……でも、全力は出し切れたかな。次は勝ちます！</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ろよ!!これがわたしだ!!</t>
+          <t xml:space="preserve">見ていただけましたか？ これが私の、全力です！</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ……!こんなはず、じゃなかったのに……っ</t>
+          <t xml:space="preserve">……悔しいです。この負けは、次で必ず取り返します！</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ……!まだ終わらない!</t>
+          <t xml:space="preserve">ふぅ……勝ちました！ 実力、見せられたかな？</t>
         </is>
       </c>
     </row>
